--- a/project/excel/excel/MonsterData.xlsx
+++ b/project/excel/excel/MonsterData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t>int</t>
   </si>
@@ -53,6 +53,9 @@
     <t>attackDis</t>
   </si>
   <si>
+    <t>expValue</t>
+  </si>
+  <si>
     <t>索引</t>
   </si>
   <si>
@@ -66,6 +69,9 @@
   </si>
   <si>
     <t>攻击距离</t>
+  </si>
+  <si>
+    <t>击杀经验值</t>
   </si>
   <si>
     <t>哥布林</t>
@@ -1002,17 +1008,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="4"/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="13.2416666666667" style="1" customWidth="1"/>
     <col min="3" max="3" width="14.3166666666667" style="1" customWidth="1"/>
     <col min="4" max="4" width="11.9333333333333" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="1"/>
+    <col min="5" max="5" width="9" style="1"/>
+    <col min="6" max="6" width="15" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1028,8 +1036,11 @@
       <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1045,30 +1056,36 @@
       <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1">
         <v>100</v>
@@ -1078,6 +1095,9 @@
       </c>
       <c r="E4" s="1">
         <v>0.1</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/project/excel/excel/MonsterData.xlsx
+++ b/project/excel/excel/MonsterData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>int</t>
   </si>
@@ -47,12 +47,6 @@
     <t>maxHp</t>
   </si>
   <si>
-    <t>attackValue</t>
-  </si>
-  <si>
-    <t>attackDis</t>
-  </si>
-  <si>
     <t>expValue</t>
   </si>
   <si>
@@ -63,12 +57,6 @@
   </si>
   <si>
     <t>最大生命值</t>
-  </si>
-  <si>
-    <t>攻击力</t>
-  </si>
-  <si>
-    <t>攻击距离</t>
   </si>
   <si>
     <t>击杀经验值</t>
@@ -1008,8 +996,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="13.2416666666667" style="1" customWidth="1"/>
@@ -1020,7 +1008,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1031,16 +1019,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1053,50 +1035,32 @@
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:4">
       <c r="A4" s="1">
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1">
         <v>100</v>
       </c>
       <c r="D4" s="1">
-        <v>20</v>
-      </c>
-      <c r="E4" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F4" s="1">
         <v>1</v>
       </c>
     </row>
